--- a/backend/resources/templates/cs-form-6.xlsx
+++ b/backend/resources/templates/cs-form-6.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\ENHS-Leave-Management-System\backend\resources\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ingia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68DFB8B-B308-4CCE-8850-A3B62DFA5816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7E8C38D-5ED0-4617-AE29-20CA3140F0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CS Form No. 6, Rev 2020 1 of 2" sheetId="2" r:id="rId1"/>
+    <sheet name="CS Form No. 6, Rev 2020 2 of 2" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'CS Form No. 6, Rev 2020 1 of 2'!$A$1:$J$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'CS Form No. 6, Rev 2020 1 of 2'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'CS Form No. 6, Rev 2020 2 of 2'!$A$1:$K$62</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
@@ -113,9 +115,6 @@
   </si>
   <si>
     <t>4.   POSITION  _____________________________     5.  SALARY  _______________</t>
-  </si>
-  <si>
-    <t>2.  NAME :            (Last)                               (First)                         (Middle)</t>
   </si>
   <si>
     <t xml:space="preserve">Terminal Leave </t>
@@ -464,6 +463,9 @@
 SCHOOL DIVISION OFFICE OF ISABELA</t>
     </r>
   </si>
+  <si>
+    <t>2.  NAME :                    (Last)                                   (First)                         (Middle)</t>
+  </si>
 </sst>
 </file>
 
@@ -632,7 +634,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -893,22 +895,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -934,6 +925,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1008,30 +1000,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1074,21 +1042,23 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1110,6 +1080,3914 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18531" cy="170560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Text Box 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="200025" y="0"/>
+          <a:ext cx="18531" cy="170560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="18288" tIns="22860" rIns="0" bIns="0" anchor="t" upright="1">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-PH" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+            <a:cs typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="76200" cy="200025"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Text Box 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7658100" y="2714625"/>
+          <a:ext cx="76200" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="18288" tIns="0" rIns="0" bIns="0" anchor="t" upright="1">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:endParaRPr lang="en-PH"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="76200" cy="200025"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Text Box 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7762875" y="4057650"/>
+          <a:ext cx="76200" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>104775</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1027" name="Check Box 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1027"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1028" name="Check Box 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1028"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>76200</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1029" name="Check Box 5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1029"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1030" name="Check Box 6" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1030"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1031" name="Check Box 7" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1031"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1032" name="Check Box 8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1032"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1033" name="Check Box 9" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1033"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1034" name="Check Box 10" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1034"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1035" name="Check Box 11" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1035"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1036" name="Check Box 12" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1036"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1037" name="Check Box 13" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1037"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1038" name="Check Box 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1038"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>2</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1039" name="Check Box 15" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1039"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1040" name="Check Box 16" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1040"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1041" name="Check Box 17" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1041"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1042" name="Check Box 18" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1042"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1043" name="Check Box 19" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1043"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1044" name="Check Box 20" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1044"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>57150</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1045" name="Check Box 21" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1045"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1046" name="Check Box 22" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1046"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1047" name="Check Box 23" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1047"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1048" name="Check Box 24" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1048"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1049" name="Check Box 25" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1049"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>28575</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>581025</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1050" name="Check Box 26" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1050"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>161925</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>590550</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1051" name="Check Box 27" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1051"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001B040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>658812</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>63501</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2952750</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>261938</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3317875" y="1952626"/>
+          <a:ext cx="4095750" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>952501</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1103312</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>261937</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="TextBox 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1254126" y="2278063"/>
+          <a:ext cx="1349374" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>970586</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1135063</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>246062</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="TextBox 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3629146" y="2211850"/>
+          <a:ext cx="1960964" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1950363</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>95230</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2649466</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>293667</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="TextBox 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6408063" y="2257405"/>
+          <a:ext cx="699103" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-PH">
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>₱</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="1">
+            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1246187</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>174624</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3032124</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>134936</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="TextBox 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5707062" y="3452812"/>
+          <a:ext cx="1785937" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1000125</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3032125</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>134937</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="TextBox 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5461000" y="3690938"/>
+          <a:ext cx="2032000" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1539875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>166688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="TextBox 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6000750" y="4159251"/>
+          <a:ext cx="1476375" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1571625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>7937</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="TextBox 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6032500" y="4413250"/>
+          <a:ext cx="1444625" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>7937</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>7937</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3024188</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="TextBox 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4294187" y="4651375"/>
+          <a:ext cx="3190876" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>738187</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2984500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>134937</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="TextBox 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5199062" y="5119688"/>
+          <a:ext cx="2246313" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>7937</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="TextBox 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4310062" y="5365750"/>
+          <a:ext cx="3167063" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>166688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>119062</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="TextBox 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="158750" y="6786563"/>
+          <a:ext cx="2619375" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>150812</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>7938</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>7937</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="TextBox 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="277812" y="7350126"/>
+          <a:ext cx="1230313" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>198437</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="TextBox 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="301625" y="7818438"/>
+          <a:ext cx="1817688" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1016001</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>7938</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>150812</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="TextBox 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1317626" y="8850313"/>
+          <a:ext cx="1785937" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1309688</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>7937</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2968625</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="TextBox 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5770563" y="9080500"/>
+          <a:ext cx="1658937" cy="198437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>23813</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="TextBox 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4484688" y="9334500"/>
+          <a:ext cx="2992437" cy="103188"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>31752</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>31749</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3024189</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>134937</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="TextBox 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4492627" y="9517062"/>
+          <a:ext cx="2992437" cy="103188"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>39689</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>23814</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3032126</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>127002</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="TextBox 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4500564" y="9683752"/>
+          <a:ext cx="2992437" cy="103188"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>277813</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>912812</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>357188</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="TextBox 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="579438" y="9977438"/>
+          <a:ext cx="2992437" cy="214313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>7937</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3000374</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>357188</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="TextBox 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4468812" y="9977438"/>
+          <a:ext cx="2992437" cy="214313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>246062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>539749</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>134936</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="TextBox 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="301625" y="10787062"/>
+          <a:ext cx="539749" cy="134937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>539749</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>134937</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="TextBox 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="301625" y="10961688"/>
+          <a:ext cx="539749" cy="134937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>539749</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>134937</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="TextBox 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="301625" y="11136313"/>
+          <a:ext cx="539749" cy="134937"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3032125</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>150812</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="TextBox 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4460875" y="10787063"/>
+          <a:ext cx="3032125" cy="150812"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3032125</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>150812</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="TextBox 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4460875" y="10961688"/>
+          <a:ext cx="3032125" cy="150812"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3032125</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>150812</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="TextBox 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4460875" y="11136313"/>
+          <a:ext cx="3032125" cy="150812"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>754062</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>492125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>785812</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>706438</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="TextBox 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2254250" y="11803063"/>
+          <a:ext cx="2992437" cy="214313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>150813</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>47627</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>889000</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>317501</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="67" name="TextBox 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="277813" y="1936752"/>
+          <a:ext cx="2111375" cy="269874"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>0</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>762000</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>123825</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4098" name="Object 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s4098"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002100000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1374,9 +5252,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.85546875" customWidth="1"/>
@@ -1385,152 +5263,141 @@
     <col min="4" max="5" width="17.42578125" customWidth="1"/>
     <col min="6" max="6" width="4.42578125" customWidth="1"/>
     <col min="7" max="8" width="2.5703125" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="24" customWidth="1"/>
-    <col min="11" max="11" width="3.28515625" customWidth="1"/>
+    <col min="9" max="9" width="46" customWidth="1"/>
+    <col min="10" max="10" width="3.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="64" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="O2" s="43"/>
-    </row>
-    <row r="3" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="59" t="s">
+    <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" s="2" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="N2" s="44"/>
+    </row>
+    <row r="3" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="1"/>
-      <c r="O3" s="43"/>
-    </row>
-    <row r="4" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="1"/>
+      <c r="N3" s="44"/>
+    </row>
+    <row r="4" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="22"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I4" s="24"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="65"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="35" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="24"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" s="37" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="35"/>
-      <c r="B8" s="69" t="s">
+      <c r="I7" s="9"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" s="38" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="36"/>
+      <c r="B8" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="36"/>
-    </row>
-    <row r="9" spans="1:15" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="37"/>
+    </row>
+    <row r="9" spans="1:14" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="14"/>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="49" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I9" s="14"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1539,376 +5406,356 @@
       <c r="F10" s="9"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I10" s="9"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="46" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
+      <c r="C11" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="48"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="28"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="1"/>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H11" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="1"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="48"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I12" s="9"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="47"/>
+      <c r="C13" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="48"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="74" t="s">
+      <c r="I13" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="73"/>
-      <c r="K13" s="1"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J13" s="1"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="48"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I14" s="48"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="47"/>
+      <c r="C15" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="48"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="J15" s="73"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I15" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="48"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I16" s="9"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="47"/>
+      <c r="C17" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="48"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="28" t="s">
+      <c r="H17" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="28"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I17" s="31"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="48"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I18" s="9"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
-      <c r="C19" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="47"/>
+      <c r="C19" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="48"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="74" t="s">
-        <v>58</v>
-      </c>
-      <c r="J19" s="73"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H19" s="51"/>
+      <c r="I19" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="48"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I20" s="48"/>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
-      <c r="C21" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="46"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="47"/>
+      <c r="C21" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="48"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="74" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" s="73"/>
-      <c r="K21" s="1"/>
+      <c r="I21" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="L21" s="2"/>
       <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-    </row>
-    <row r="22" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="48"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="1"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="46"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="47"/>
+      <c r="C23" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="48"/>
       <c r="H23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="26"/>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I23" s="27"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="48"/>
       <c r="G24" s="2"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="1"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="1"/>
+      <c r="L24" s="2"/>
       <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-    </row>
-    <row r="25" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="47"/>
+      <c r="C25" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="48"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="28" t="s">
+      <c r="H25" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="28"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="1"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="1"/>
+      <c r="L25" s="2"/>
       <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-    </row>
-    <row r="26" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="48"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="1"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-    </row>
-    <row r="27" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="47"/>
+      <c r="C27" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="48"/>
       <c r="G27" s="2"/>
       <c r="H27" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="I27" s="27"/>
+      <c r="J27" s="1"/>
+      <c r="L27" s="2"/>
       <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-    </row>
-    <row r="28" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="47"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48"/>
       <c r="G28" s="2"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="1"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-    </row>
-    <row r="29" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="47"/>
+      <c r="C29" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48"/>
       <c r="G29" s="2"/>
       <c r="H29" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="26"/>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I29" s="27"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="48"/>
       <c r="G30" s="2"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="1"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="1"/>
+      <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-    </row>
-    <row r="31" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="60" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="61"/>
+      <c r="C31" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
       <c r="G31" s="2"/>
-      <c r="H31" s="28" t="s">
+      <c r="H31" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="28"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="1"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="1"/>
+      <c r="L31" s="2"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-    </row>
-    <row r="32" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="48"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="1"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-    </row>
-    <row r="33" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="47"/>
+      <c r="C33" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="48"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="J33" s="75"/>
-      <c r="K33" s="1"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="L33" s="2"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-    </row>
-    <row r="34" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -1917,54 +5764,51 @@
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I34" s="48"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="46" t="s">
-        <v>57</v>
+      <c r="C35" s="47" t="s">
+        <v>56</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="47" t="s">
+      <c r="I35" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="J35" s="75"/>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="46"/>
+      <c r="C36" s="47"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
       <c r="G36" s="2"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="1"/>
-    </row>
-    <row r="37" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I36" s="27"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="46"/>
+      <c r="C37" s="47"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="28" t="s">
+      <c r="H37" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="I37" s="28"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="1"/>
-    </row>
-    <row r="38" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I37" s="9"/>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1973,14 +5817,13 @@
       <c r="F38" s="9"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="1"/>
-    </row>
-    <row r="39" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I38" s="9"/>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
-      <c r="B39" s="28" t="s">
-        <v>43</v>
+      <c r="B39" s="29" t="s">
+        <v>42</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1988,13 +5831,12 @@
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="47" t="s">
+      <c r="I39" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="J39" s="75"/>
-      <c r="K39" s="1"/>
-    </row>
-    <row r="40" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2003,14 +5845,13 @@
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="47"/>
-      <c r="K40" s="1"/>
-    </row>
-    <row r="41" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I40" s="48"/>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
-      <c r="B41" s="28" t="s">
-        <v>44</v>
+      <c r="B41" s="29" t="s">
+        <v>43</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -2018,26 +5859,24 @@
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="J41" s="26"/>
-      <c r="K41" s="1"/>
-    </row>
-    <row r="42" spans="1:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I41" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:13" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
-      <c r="F42" s="20"/>
+      <c r="F42" s="21"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="1"/>
-    </row>
-    <row r="43" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I42" s="21"/>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
         <v>7</v>
       </c>
@@ -2046,26 +5885,26 @@
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="9"/>
-      <c r="G43" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="J43" s="26"/>
-      <c r="K43" s="1"/>
-    </row>
-    <row r="44" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G43" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="I43" s="27"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="10"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="19"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="1"/>
-    </row>
-    <row r="45" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G44" s="20"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="32" t="s">
         <v>25</v>
       </c>
       <c r="C45" s="2"/>
@@ -2074,28 +5913,26 @@
       <c r="F45" s="9"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
-      <c r="I45" s="76" t="s">
+      <c r="I45" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="J45" s="26"/>
-      <c r="K45" s="1"/>
-    </row>
-    <row r="46" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="2"/>
-      <c r="C46" s="21"/>
+      <c r="C46" s="22"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="9"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="1"/>
-    </row>
-    <row r="47" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I46" s="48"/>
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
-      <c r="B47" s="31"/>
+      <c r="B47" s="32"/>
       <c r="C47" s="2" t="s">
         <v>17</v>
       </c>
@@ -2104,58 +5941,54 @@
       <c r="F47" s="9"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-      <c r="I47" s="76" t="s">
+      <c r="I47" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="26"/>
-      <c r="K47" s="1"/>
-    </row>
-    <row r="48" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
-      <c r="B48" s="33" t="s">
+      <c r="B48" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
       <c r="F48" s="9"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="78"/>
-      <c r="J48" s="77"/>
-      <c r="K48" s="1"/>
-    </row>
-    <row r="49" spans="1:11" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I48" s="19"/>
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:10" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="71" t="s">
+      <c r="G49" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="H49" s="67"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="68"/>
-      <c r="K49" s="1"/>
-    </row>
-    <row r="50" spans="1:11" s="37" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="35"/>
-      <c r="B50" s="69" t="s">
+      <c r="H49" s="60"/>
+      <c r="I49" s="61"/>
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:10" s="38" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="36"/>
+      <c r="B50" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C50" s="69"/>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="69"/>
-      <c r="H50" s="69"/>
-      <c r="I50" s="69"/>
-      <c r="J50" s="70"/>
-      <c r="K50" s="36"/>
-    </row>
-    <row r="51" spans="1:11" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="62"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="63"/>
+      <c r="J50" s="37"/>
+    </row>
+    <row r="51" spans="1:10" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>9</v>
       </c>
@@ -2168,11 +6001,10 @@
         <v>10</v>
       </c>
       <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="1"/>
-    </row>
-    <row r="52" spans="1:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I51" s="14"/>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -2181,27 +6013,25 @@
       <c r="F52" s="9"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="1"/>
-    </row>
-    <row r="53" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I52" s="9"/>
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8"/>
-      <c r="C53" s="44" t="s">
-        <v>41</v>
+      <c r="C53" s="45" t="s">
+        <v>40</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="9"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="9" t="s">
+      <c r="I53" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K53" s="1"/>
-    </row>
-    <row r="54" spans="1:11" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="8"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2210,81 +6040,76 @@
       <c r="F54" s="9"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="1"/>
-    </row>
-    <row r="55" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I54" s="9"/>
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="8"/>
       <c r="B55" s="2"/>
       <c r="C55" s="15"/>
       <c r="D55" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" s="16" t="s">
         <v>35</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>36</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="K55" s="1"/>
-    </row>
-    <row r="56" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I55" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="8"/>
       <c r="B56" s="2"/>
-      <c r="C56" s="45" t="s">
-        <v>37</v>
+      <c r="C56" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="D56" s="17"/>
       <c r="E56" s="17"/>
       <c r="F56" s="9"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K56" s="1"/>
-    </row>
-    <row r="57" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I56" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="8"/>
       <c r="B57" s="2"/>
-      <c r="C57" s="45" t="s">
-        <v>38</v>
+      <c r="C57" s="46" t="s">
+        <v>37</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="17"/>
       <c r="F57" s="9"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K57" s="1"/>
-    </row>
-    <row r="58" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I57" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="8"/>
       <c r="B58" s="2"/>
-      <c r="C58" s="45" t="s">
-        <v>39</v>
+      <c r="C58" s="46" t="s">
+        <v>38</v>
       </c>
       <c r="D58" s="17"/>
       <c r="E58" s="17"/>
       <c r="F58" s="9"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K58" s="1"/>
-    </row>
-    <row r="59" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I58" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="8"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2293,30 +6118,28 @@
       <c r="F59" s="2"/>
       <c r="G59" s="8"/>
       <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K59" s="1"/>
-    </row>
-    <row r="60" spans="1:11" s="42" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="38"/>
-      <c r="B60" s="39"/>
-      <c r="C60" s="65" t="s">
+      <c r="I59" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" s="43" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="39"/>
+      <c r="B60" s="40"/>
+      <c r="C60" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="D60" s="65"/>
-      <c r="E60" s="65"/>
-      <c r="F60" s="40"/>
-      <c r="G60" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H60" s="67"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="68"/>
-      <c r="K60" s="41"/>
-    </row>
-    <row r="61" spans="1:11" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="41"/>
+      <c r="G60" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="H60" s="60"/>
+      <c r="I60" s="61"/>
+      <c r="J60" s="42"/>
+    </row>
+    <row r="61" spans="1:10" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>11</v>
       </c>
@@ -2329,11 +6152,10 @@
         <v>12</v>
       </c>
       <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="1"/>
-    </row>
-    <row r="62" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I61" s="14"/>
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="8"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
@@ -2343,13 +6165,12 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="K62" s="1"/>
-    </row>
-    <row r="63" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I62" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="8"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
@@ -2359,13 +6180,12 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K63" s="1"/>
-    </row>
-    <row r="64" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I63" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="8"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2" t="s">
@@ -2375,125 +6195,715 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K64" s="1"/>
-    </row>
-    <row r="65" spans="1:10" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="B65" s="56"/>
-      <c r="C65" s="56"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
-      <c r="H65" s="56"/>
-      <c r="I65" s="56"/>
-      <c r="J65" s="57"/>
-    </row>
-    <row r="66" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A66" s="29"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
-    </row>
-    <row r="67" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="58"/>
-      <c r="B67" s="58"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="58"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58"/>
-      <c r="I67" s="58"/>
-      <c r="J67" s="58"/>
-    </row>
-    <row r="68" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="58"/>
-      <c r="B68" s="58"/>
-      <c r="C68" s="58"/>
-      <c r="D68" s="58"/>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58"/>
-      <c r="I68" s="58"/>
-      <c r="J68" s="58"/>
-    </row>
-    <row r="69" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="58"/>
-      <c r="B69" s="58"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="58"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="58"/>
-      <c r="I69" s="58"/>
-      <c r="J69" s="58"/>
-    </row>
-    <row r="70" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="58"/>
-      <c r="B70" s="58"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="58"/>
-      <c r="E70" s="58"/>
-      <c r="F70" s="58"/>
-      <c r="G70" s="58"/>
-      <c r="H70" s="58"/>
-      <c r="I70" s="58"/>
-      <c r="J70" s="58"/>
-    </row>
-    <row r="71" spans="1:10" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="58"/>
-      <c r="B71" s="58"/>
-      <c r="C71" s="58"/>
-      <c r="D71" s="58"/>
-      <c r="E71" s="58"/>
-      <c r="F71" s="58"/>
-      <c r="G71" s="58"/>
-      <c r="H71" s="58"/>
-      <c r="I71" s="58"/>
-      <c r="J71" s="58"/>
+      <c r="I64" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" s="69"/>
+      <c r="C65" s="69"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="69"/>
+      <c r="F65" s="69"/>
+      <c r="G65" s="69"/>
+      <c r="H65" s="69"/>
+      <c r="I65" s="70"/>
+    </row>
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="A66" s="30"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+    </row>
+    <row r="67" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="71"/>
+      <c r="B67" s="71"/>
+      <c r="C67" s="71"/>
+      <c r="D67" s="71"/>
+      <c r="E67" s="71"/>
+      <c r="F67" s="71"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="71"/>
+      <c r="I67" s="71"/>
+    </row>
+    <row r="68" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="71"/>
+      <c r="B68" s="71"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
+      <c r="G68" s="71"/>
+      <c r="H68" s="71"/>
+      <c r="I68" s="71"/>
+    </row>
+    <row r="69" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="71"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="71"/>
+      <c r="D69" s="71"/>
+      <c r="E69" s="71"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="71"/>
+      <c r="H69" s="71"/>
+      <c r="I69" s="71"/>
+    </row>
+    <row r="70" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="71"/>
+      <c r="B70" s="71"/>
+      <c r="C70" s="71"/>
+      <c r="D70" s="71"/>
+      <c r="E70" s="71"/>
+      <c r="F70" s="71"/>
+      <c r="G70" s="71"/>
+      <c r="H70" s="71"/>
+      <c r="I70" s="71"/>
+    </row>
+    <row r="71" spans="1:9" s="28" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="71"/>
+      <c r="B71" s="71"/>
+      <c r="C71" s="71"/>
+      <c r="D71" s="71"/>
+      <c r="E71" s="71"/>
+      <c r="F71" s="71"/>
+      <c r="G71" s="71"/>
+      <c r="H71" s="71"/>
+      <c r="I71" s="71"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="A3:J3"/>
+  <mergeCells count="17">
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C60:E60"/>
-    <mergeCell ref="G60:J60"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="G49:J49"/>
-    <mergeCell ref="B50:J50"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A65:J65"/>
-    <mergeCell ref="A67:J67"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="A69:J69"/>
-    <mergeCell ref="A71:J71"/>
-    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="G60:I60"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:I5"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1027" r:id="rId4" name="Check Box 3">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>104775</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>581025</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1028" r:id="rId5" name="Check Box 4">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>581025</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1029" r:id="rId6" name="Check Box 5">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>76200</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>9525</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1030" r:id="rId7" name="Check Box 6">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>581025</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1031" r:id="rId8" name="Check Box 7">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>581025</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>9525</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1032" r:id="rId9" name="Check Box 8">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>581025</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>9525</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1033" r:id="rId10" name="Check Box 9">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1034" r:id="rId11" name="Check Box 10">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1035" r:id="rId12" name="Check Box 11">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1036" r:id="rId13" name="Check Box 12">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1037" r:id="rId14" name="Check Box 13">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>581025</xdr:colOff>
+                    <xdr:row>31</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1038" r:id="rId15" name="Check Box 14">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>31</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>33</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1039" r:id="rId16" name="Check Box 15">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>114300</xdr:colOff>
+                    <xdr:row>33</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>2</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>35</xdr:row>
+                    <xdr:rowOff>9525</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1040" r:id="rId17" name="Check Box 16">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1041" r:id="rId18" name="Check Box 17">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>15</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1042" r:id="rId19" name="Check Box 18">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>9525</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1043" r:id="rId20" name="Check Box 19">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>581025</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>9525</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1044" r:id="rId21" name="Check Box 20">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>31</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>581025</xdr:colOff>
+                    <xdr:row>33</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1045" r:id="rId22" name="Check Box 21">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>33</xdr:row>
+                    <xdr:rowOff>57150</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>35</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1046" r:id="rId23" name="Check Box 22">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>37</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>39</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1047" r:id="rId24" name="Check Box 23">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>39</xdr:row>
+                    <xdr:rowOff>38100</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>41</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1048" r:id="rId25" name="Check Box 24">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>43</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>45</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1049" r:id="rId26" name="Check Box 25">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>45</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>47</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1050" r:id="rId27" name="Check Box 26">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>28575</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>581025</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>9525</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1051" r:id="rId28" name="Check Box 27">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>161925</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>47625</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>8</xdr:col>
+                    <xdr:colOff>590550</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="81" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <oleObjects>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Document" shapeId="4098" r:id="rId4">
+          <objectPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>762000</xdr:colOff>
+                <xdr:row>61</xdr:row>
+                <xdr:rowOff>123825</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Document" shapeId="4098" r:id="rId4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </oleObjects>
 </worksheet>
 </file>
--- a/backend/resources/templates/cs-form-6.xlsx
+++ b/backend/resources/templates/cs-form-6.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ingia\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\ENHS-Leave-Management-System\backend\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7E8C38D-5ED0-4617-AE29-20CA3140F0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0E6ED1-9842-4998-904B-D2BFF2B91DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="CS Form No. 6, Rev 2020 2 of 2" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'CS Form No. 6, Rev 2020 1 of 2'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'CS Form No. 6, Rev 2020 1 of 2'!$A$1:$I$66</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'CS Form No. 6, Rev 2020 2 of 2'!$A$1:$K$62</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -390,9 +390,6 @@
     <t>Abroad (Specify) _____________________________</t>
   </si>
   <si>
-    <t>School Principal I</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">
 _________________________________
@@ -465,6 +462,9 @@
   </si>
   <si>
     <t>2.  NAME :                    (Last)                                   (First)                         (Middle)</t>
+  </si>
+  <si>
+    <t>School Principal II</t>
   </si>
 </sst>
 </file>
@@ -899,7 +899,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -938,9 +938,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -1000,6 +997,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1047,18 +1065,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3250,13 +3256,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1950363</xdr:colOff>
+      <xdr:colOff>1804572</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>95230</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2649466</xdr:colOff>
+      <xdr:colOff>2503675</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>293667</xdr:rowOff>
     </xdr:to>
@@ -3273,7 +3279,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6408063" y="2257405"/>
+          <a:off x="6275490" y="2252934"/>
           <a:ext cx="699103" cy="198437"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4347,16 +4353,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>7937</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>75974</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>217714</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3000374</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>357188</xdr:rowOff>
+      <xdr:colOff>2898321</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>10206</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4371,15 +4377,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4468812" y="9977438"/>
+          <a:off x="4355420" y="10048875"/>
           <a:ext cx="2992437" cy="214313"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
+        <a:noFill/>
         <a:ln w="9525" cmpd="sng">
           <a:noFill/>
         </a:ln>
@@ -4403,7 +4407,24 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>EMILY O.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> BENITEZ</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="1">
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4915,6 +4936,153 @@
         <a:lstStyle/>
         <a:p>
           <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>316819</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>240846</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>948417</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609373" y="10072007"/>
+          <a:ext cx="2992437" cy="214313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>PRECIOUS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t> C. PABON</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="1">
+            <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>772660</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>615042</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>805543</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>829355</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2262642" y="11908971"/>
+          <a:ext cx="2992437" cy="214313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>RACHELE R. LLANA, PhD, CESO V</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5268,47 +5436,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="50"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="49"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="N2" s="44"/>
+      <c r="A2" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="N2" s="43"/>
     </row>
     <row r="3" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
       <c r="J3" s="1"/>
-      <c r="N3" s="44"/>
+      <c r="N3" s="43"/>
     </row>
     <row r="4" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -5318,7 +5486,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="23"/>
       <c r="E4" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -5330,14 +5498,14 @@
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="67"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="73"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5347,7 +5515,7 @@
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="34" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="4"/>
@@ -5367,19 +5535,19 @@
       <c r="I7" s="9"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:14" s="38" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
-      <c r="B8" s="62" t="s">
+    <row r="8" spans="1:14" s="37" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="35"/>
+      <c r="B8" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="37"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="36"/>
     </row>
     <row r="9" spans="1:14" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
@@ -5390,7 +5558,7 @@
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="14"/>
-      <c r="G9" s="49" t="s">
+      <c r="G9" s="48" t="s">
         <v>18</v>
       </c>
       <c r="H9" s="13"/>
@@ -5412,12 +5580,12 @@
     <row r="11" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="48"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47"/>
       <c r="G11" s="2"/>
       <c r="H11" s="29" t="s">
         <v>31</v>
@@ -5429,10 +5597,10 @@
     <row r="12" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="47"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="9"/>
@@ -5441,15 +5609,15 @@
     <row r="13" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="48"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="47"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-      <c r="I13" s="48" t="s">
+      <c r="I13" s="47" t="s">
         <v>14</v>
       </c>
       <c r="J13" s="1"/>
@@ -5458,27 +5626,27 @@
     <row r="14" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="2"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="48"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="47"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-      <c r="I14" s="48"/>
+      <c r="I14" s="47"/>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="48"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="47"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="48" t="s">
+      <c r="I15" s="47" t="s">
         <v>64</v>
       </c>
       <c r="J15" s="1"/>
@@ -5486,10 +5654,10 @@
     <row r="16" spans="1:14" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="47"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="9"/>
@@ -5498,26 +5666,26 @@
     <row r="17" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="48"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="47"/>
       <c r="G17" s="2"/>
       <c r="H17" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="31"/>
+      <c r="I17" s="30"/>
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="47"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="9"/>
@@ -5525,15 +5693,15 @@
     </row>
     <row r="19" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="48"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="47"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="48" t="s">
+      <c r="H19" s="50"/>
+      <c r="I19" s="47" t="s">
         <v>57</v>
       </c>
       <c r="J19" s="1"/>
@@ -5541,26 +5709,26 @@
     <row r="20" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="48"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="47"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="48"/>
+      <c r="I20" s="47"/>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="47"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="48" t="s">
+      <c r="I21" s="47" t="s">
         <v>63</v>
       </c>
       <c r="J21" s="1"/>
@@ -5570,10 +5738,10 @@
     <row r="22" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="48"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="47"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="9"/>
@@ -5585,12 +5753,12 @@
     <row r="23" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="48"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="47"/>
       <c r="H23" s="2" t="s">
         <v>24</v>
       </c>
@@ -5600,10 +5768,10 @@
     <row r="24" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="48"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="47"/>
       <c r="G24" s="2"/>
       <c r="I24" s="27"/>
       <c r="J24" s="1"/>
@@ -5613,12 +5781,12 @@
     <row r="25" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="48"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="47"/>
       <c r="G25" s="2"/>
       <c r="H25" s="29" t="s">
         <v>22</v>
@@ -5631,10 +5799,10 @@
     <row r="26" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="47"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="27"/>
@@ -5646,12 +5814,12 @@
     <row r="27" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="48"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="47"/>
       <c r="G27" s="2"/>
       <c r="H27" s="9" t="s">
         <v>58</v>
@@ -5664,10 +5832,10 @@
     <row r="28" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="48"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="47"/>
       <c r="G28" s="2"/>
       <c r="I28" s="27"/>
       <c r="J28" s="1"/>
@@ -5678,12 +5846,12 @@
     <row r="29" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="47" t="s">
+      <c r="C29" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="47"/>
       <c r="G29" s="2"/>
       <c r="H29" t="s">
         <v>24</v>
@@ -5694,10 +5862,10 @@
     <row r="30" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="48"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="47"/>
       <c r="G30" s="2"/>
       <c r="I30" s="27"/>
       <c r="J30" s="1"/>
@@ -5707,12 +5875,12 @@
     <row r="31" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="53" t="s">
+      <c r="C31" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="54"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="60"/>
       <c r="G31" s="2"/>
       <c r="H31" s="29" t="s">
         <v>20</v>
@@ -5725,10 +5893,10 @@
     <row r="32" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="48"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="47"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="9"/>
@@ -5740,15 +5908,15 @@
     <row r="33" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="48"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="47"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="48" t="s">
+      <c r="H33" s="50"/>
+      <c r="I33" s="47" t="s">
         <v>32</v>
       </c>
       <c r="J33" s="1"/>
@@ -5764,13 +5932,13 @@
       <c r="F34" s="9"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="48"/>
+      <c r="I34" s="47"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="47" t="s">
+      <c r="C35" s="46" t="s">
         <v>56</v>
       </c>
       <c r="D35" s="2"/>
@@ -5778,7 +5946,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="48" t="s">
+      <c r="I35" s="47" t="s">
         <v>21</v>
       </c>
       <c r="J35" s="1"/>
@@ -5786,7 +5954,7 @@
     <row r="36" spans="1:13" ht="5.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="47"/>
+      <c r="C36" s="46"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="9"/>
@@ -5797,7 +5965,7 @@
     <row r="37" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="47"/>
+      <c r="C37" s="46"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="9"/>
@@ -5831,7 +5999,7 @@
       <c r="F39" s="9"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="48" t="s">
+      <c r="I39" s="47" t="s">
         <v>16</v>
       </c>
       <c r="J39" s="1"/>
@@ -5845,7 +6013,7 @@
       <c r="F40" s="9"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="48"/>
+      <c r="I40" s="47"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5859,7 +6027,7 @@
       <c r="F41" s="9"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="48" t="s">
+      <c r="I41" s="47" t="s">
         <v>30</v>
       </c>
       <c r="J41" s="1"/>
@@ -5904,7 +6072,7 @@
     </row>
     <row r="45" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
-      <c r="B45" s="32" t="s">
+      <c r="B45" s="31" t="s">
         <v>25</v>
       </c>
       <c r="C45" s="2"/>
@@ -5913,7 +6081,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
-      <c r="I45" s="48" t="s">
+      <c r="I45" s="47" t="s">
         <v>2</v>
       </c>
       <c r="J45" s="1"/>
@@ -5927,12 +6095,12 @@
       <c r="F46" s="9"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="48"/>
+      <c r="I46" s="47"/>
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
-      <c r="B47" s="32"/>
+      <c r="B47" s="31"/>
       <c r="C47" s="2" t="s">
         <v>17</v>
       </c>
@@ -5941,19 +6109,19 @@
       <c r="F47" s="9"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-      <c r="I47" s="48" t="s">
+      <c r="I47" s="47" t="s">
         <v>3</v>
       </c>
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
-      <c r="B48" s="34" t="s">
+      <c r="B48" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
       <c r="F48" s="9"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -5967,26 +6135,26 @@
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="64" t="s">
+      <c r="G49" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="H49" s="60"/>
-      <c r="I49" s="61"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="67"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:10" s="38" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="36"/>
-      <c r="B50" s="62" t="s">
+    <row r="50" spans="1:10" s="37" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="35"/>
+      <c r="B50" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C50" s="62"/>
-      <c r="D50" s="62"/>
-      <c r="E50" s="62"/>
-      <c r="F50" s="62"/>
-      <c r="G50" s="62"/>
-      <c r="H50" s="62"/>
-      <c r="I50" s="63"/>
-      <c r="J50" s="37"/>
+      <c r="C50" s="68"/>
+      <c r="D50" s="68"/>
+      <c r="E50" s="68"/>
+      <c r="F50" s="68"/>
+      <c r="G50" s="68"/>
+      <c r="H50" s="68"/>
+      <c r="I50" s="69"/>
+      <c r="J50" s="36"/>
     </row>
     <row r="51" spans="1:10" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
@@ -6018,7 +6186,7 @@
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8"/>
-      <c r="C53" s="45" t="s">
+      <c r="C53" s="44" t="s">
         <v>40</v>
       </c>
       <c r="D53" s="2"/>
@@ -6064,7 +6232,7 @@
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="8"/>
       <c r="B56" s="2"/>
-      <c r="C56" s="46" t="s">
+      <c r="C56" s="45" t="s">
         <v>36</v>
       </c>
       <c r="D56" s="17"/>
@@ -6080,7 +6248,7 @@
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="8"/>
       <c r="B57" s="2"/>
-      <c r="C57" s="46" t="s">
+      <c r="C57" s="45" t="s">
         <v>37</v>
       </c>
       <c r="D57" s="17"/>
@@ -6096,7 +6264,7 @@
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="8"/>
       <c r="B58" s="2"/>
-      <c r="C58" s="46" t="s">
+      <c r="C58" s="45" t="s">
         <v>38</v>
       </c>
       <c r="D58" s="17"/>
@@ -6123,21 +6291,21 @@
       </c>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10" s="43" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="39"/>
-      <c r="B60" s="40"/>
-      <c r="C60" s="58" t="s">
+    <row r="60" spans="1:10" s="42" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="38"/>
+      <c r="B60" s="39"/>
+      <c r="C60" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="D60" s="58"/>
-      <c r="E60" s="58"/>
-      <c r="F60" s="41"/>
-      <c r="G60" s="59" t="s">
-        <v>65</v>
-      </c>
-      <c r="H60" s="60"/>
-      <c r="I60" s="61"/>
-      <c r="J60" s="42"/>
+      <c r="D60" s="64"/>
+      <c r="E60" s="64"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="65" t="s">
+        <v>68</v>
+      </c>
+      <c r="H60" s="66"/>
+      <c r="I60" s="67"/>
+      <c r="J60" s="41"/>
     </row>
     <row r="61" spans="1:10" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
@@ -6201,92 +6369,86 @@
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="68" t="s">
-        <v>66</v>
-      </c>
-      <c r="B65" s="69"/>
-      <c r="C65" s="69"/>
-      <c r="D65" s="69"/>
-      <c r="E65" s="69"/>
-      <c r="F65" s="69"/>
-      <c r="G65" s="69"/>
-      <c r="H65" s="69"/>
-      <c r="I65" s="70"/>
+      <c r="A65" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65" s="55"/>
+      <c r="C65" s="55"/>
+      <c r="D65" s="55"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="55"/>
+      <c r="G65" s="55"/>
+      <c r="H65" s="55"/>
+      <c r="I65" s="56"/>
     </row>
     <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A66" s="30"/>
-      <c r="B66" s="30"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
-      <c r="H66" s="30"/>
-      <c r="I66" s="30"/>
+      <c r="A66" s="52"/>
+      <c r="B66" s="51"/>
+      <c r="C66" s="51"/>
+      <c r="D66" s="51"/>
+      <c r="E66" s="51"/>
+      <c r="F66" s="51"/>
+      <c r="G66" s="51"/>
+      <c r="H66" s="51"/>
+      <c r="I66" s="53"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="71"/>
-      <c r="B67" s="71"/>
-      <c r="C67" s="71"/>
-      <c r="D67" s="71"/>
-      <c r="E67" s="71"/>
-      <c r="F67" s="71"/>
-      <c r="G67" s="71"/>
-      <c r="H67" s="71"/>
-      <c r="I67" s="71"/>
+      <c r="A67" s="57"/>
+      <c r="B67" s="57"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
     </row>
     <row r="68" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="71"/>
-      <c r="B68" s="71"/>
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="71"/>
-      <c r="F68" s="71"/>
-      <c r="G68" s="71"/>
-      <c r="H68" s="71"/>
-      <c r="I68" s="71"/>
+      <c r="A68" s="57"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="57"/>
     </row>
     <row r="69" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="71"/>
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="71"/>
-      <c r="E69" s="71"/>
-      <c r="F69" s="71"/>
-      <c r="G69" s="71"/>
-      <c r="H69" s="71"/>
-      <c r="I69" s="71"/>
+      <c r="A69" s="57"/>
+      <c r="B69" s="57"/>
+      <c r="C69" s="57"/>
+      <c r="D69" s="57"/>
+      <c r="E69" s="57"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="57"/>
+      <c r="H69" s="57"/>
+      <c r="I69" s="57"/>
     </row>
     <row r="70" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="71"/>
-      <c r="B70" s="71"/>
-      <c r="C70" s="71"/>
-      <c r="D70" s="71"/>
-      <c r="E70" s="71"/>
-      <c r="F70" s="71"/>
-      <c r="G70" s="71"/>
-      <c r="H70" s="71"/>
-      <c r="I70" s="71"/>
+      <c r="A70" s="57"/>
+      <c r="B70" s="57"/>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="57"/>
     </row>
     <row r="71" spans="1:9" s="28" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="71"/>
-      <c r="B71" s="71"/>
-      <c r="C71" s="71"/>
-      <c r="D71" s="71"/>
-      <c r="E71" s="71"/>
-      <c r="F71" s="71"/>
-      <c r="G71" s="71"/>
-      <c r="H71" s="71"/>
-      <c r="I71" s="71"/>
+      <c r="A71" s="57"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="57"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="57"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A70:I70"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="A2:I2"/>
@@ -6298,6 +6460,12 @@
     <mergeCell ref="B50:I50"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="E5:I5"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A70:I70"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0" header="0.5" footer="0.5"/>

--- a/backend/resources/templates/cs-form-6.xlsx
+++ b/backend/resources/templates/cs-form-6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Capstone\ENHS-Leave-Management-System\backend\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0E6ED1-9842-4998-904B-D2BFF2B91DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535FD2B8-9BFF-4FFC-9555-B79811DB89FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1006,18 +1006,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1065,6 +1053,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3969,70 +3969,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1016001</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>7938</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>150812</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="TextBox 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1317626" y="8850313"/>
-          <a:ext cx="1785937" cy="198437"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1309688</xdr:colOff>
       <xdr:row>53</xdr:row>
@@ -4425,198 +4361,6 @@
             <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
           </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>246062</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>539749</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>134936</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="60" name="TextBox 59">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="301625" y="10787062"/>
-          <a:ext cx="539749" cy="134937"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>539749</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>134937</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="61" name="TextBox 60">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="301625" y="10961688"/>
-          <a:ext cx="539749" cy="134937"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>539749</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>134937</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="62" name="TextBox 61">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="301625" y="11136313"/>
-          <a:ext cx="539749" cy="134937"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -5436,45 +5180,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
       <c r="I1" s="49"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
       <c r="N2" s="43"/>
     </row>
     <row r="3" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
       <c r="J3" s="1"/>
       <c r="N3" s="43"/>
     </row>
@@ -5498,14 +5242,14 @@
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="73"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="69"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5537,16 +5281,16 @@
     </row>
     <row r="8" spans="1:14" s="37" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35"/>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="69"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="65"/>
       <c r="J8" s="36"/>
     </row>
     <row r="9" spans="1:14" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -5875,12 +5619,12 @@
     <row r="31" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="59" t="s">
+      <c r="C31" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="60"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="56"/>
       <c r="G31" s="2"/>
       <c r="H31" s="29" t="s">
         <v>20</v>
@@ -6135,25 +5879,25 @@
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="9"/>
-      <c r="G49" s="70" t="s">
+      <c r="G49" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="H49" s="66"/>
-      <c r="I49" s="67"/>
+      <c r="H49" s="62"/>
+      <c r="I49" s="63"/>
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10" s="37" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="35"/>
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="C50" s="68"/>
-      <c r="D50" s="68"/>
-      <c r="E50" s="68"/>
-      <c r="F50" s="68"/>
-      <c r="G50" s="68"/>
-      <c r="H50" s="68"/>
-      <c r="I50" s="69"/>
+      <c r="C50" s="64"/>
+      <c r="D50" s="64"/>
+      <c r="E50" s="64"/>
+      <c r="F50" s="64"/>
+      <c r="G50" s="64"/>
+      <c r="H50" s="64"/>
+      <c r="I50" s="65"/>
       <c r="J50" s="36"/>
     </row>
     <row r="51" spans="1:10" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -6294,17 +6038,17 @@
     <row r="60" spans="1:10" s="42" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="38"/>
       <c r="B60" s="39"/>
-      <c r="C60" s="64" t="s">
+      <c r="C60" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
+      <c r="D60" s="60"/>
+      <c r="E60" s="60"/>
       <c r="F60" s="40"/>
-      <c r="G60" s="65" t="s">
+      <c r="G60" s="61" t="s">
         <v>68</v>
       </c>
-      <c r="H60" s="66"/>
-      <c r="I60" s="67"/>
+      <c r="H60" s="62"/>
+      <c r="I60" s="63"/>
       <c r="J60" s="41"/>
     </row>
     <row r="61" spans="1:10" ht="19.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -6369,17 +6113,17 @@
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="54" t="s">
+      <c r="A65" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="55"/>
-      <c r="C65" s="55"/>
-      <c r="D65" s="55"/>
-      <c r="E65" s="55"/>
-      <c r="F65" s="55"/>
-      <c r="G65" s="55"/>
-      <c r="H65" s="55"/>
-      <c r="I65" s="56"/>
+      <c r="B65" s="71"/>
+      <c r="C65" s="71"/>
+      <c r="D65" s="71"/>
+      <c r="E65" s="71"/>
+      <c r="F65" s="71"/>
+      <c r="G65" s="71"/>
+      <c r="H65" s="71"/>
+      <c r="I65" s="72"/>
     </row>
     <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="52"/>
@@ -6393,62 +6137,68 @@
       <c r="I66" s="53"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="57"/>
-      <c r="B67" s="57"/>
-      <c r="C67" s="57"/>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="57"/>
+      <c r="A67" s="73"/>
+      <c r="B67" s="73"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="73"/>
+      <c r="G67" s="73"/>
+      <c r="H67" s="73"/>
+      <c r="I67" s="73"/>
     </row>
     <row r="68" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="57"/>
-      <c r="B68" s="57"/>
-      <c r="C68" s="57"/>
-      <c r="D68" s="57"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="57"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="57"/>
-      <c r="I68" s="57"/>
+      <c r="A68" s="73"/>
+      <c r="B68" s="73"/>
+      <c r="C68" s="73"/>
+      <c r="D68" s="73"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="73"/>
+      <c r="H68" s="73"/>
+      <c r="I68" s="73"/>
     </row>
     <row r="69" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="57"/>
-      <c r="B69" s="57"/>
-      <c r="C69" s="57"/>
-      <c r="D69" s="57"/>
-      <c r="E69" s="57"/>
-      <c r="F69" s="57"/>
-      <c r="G69" s="57"/>
-      <c r="H69" s="57"/>
-      <c r="I69" s="57"/>
+      <c r="A69" s="73"/>
+      <c r="B69" s="73"/>
+      <c r="C69" s="73"/>
+      <c r="D69" s="73"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="73"/>
+      <c r="G69" s="73"/>
+      <c r="H69" s="73"/>
+      <c r="I69" s="73"/>
     </row>
     <row r="70" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="57"/>
-      <c r="B70" s="57"/>
-      <c r="C70" s="57"/>
-      <c r="D70" s="57"/>
-      <c r="E70" s="57"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
+      <c r="A70" s="73"/>
+      <c r="B70" s="73"/>
+      <c r="C70" s="73"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="73"/>
+      <c r="F70" s="73"/>
+      <c r="G70" s="73"/>
+      <c r="H70" s="73"/>
+      <c r="I70" s="73"/>
     </row>
     <row r="71" spans="1:9" s="28" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="57"/>
-      <c r="B71" s="57"/>
-      <c r="C71" s="57"/>
-      <c r="D71" s="57"/>
-      <c r="E71" s="57"/>
-      <c r="F71" s="57"/>
-      <c r="G71" s="57"/>
-      <c r="H71" s="57"/>
-      <c r="I71" s="57"/>
+      <c r="A71" s="73"/>
+      <c r="B71" s="73"/>
+      <c r="C71" s="73"/>
+      <c r="D71" s="73"/>
+      <c r="E71" s="73"/>
+      <c r="F71" s="73"/>
+      <c r="G71" s="73"/>
+      <c r="H71" s="73"/>
+      <c r="I71" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A70:I70"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="A2:I2"/>
@@ -6460,12 +6210,6 @@
     <mergeCell ref="B50:I50"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="E5:I5"/>
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="A70:I70"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.5" right="0.5" top="0.25" bottom="0" header="0.5" footer="0.5"/>
